--- a/tests/data/written.xlsx
+++ b/tests/data/written.xlsx
@@ -440,9 +440,6 @@
       <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="C4">
-        <v>1.8</v>
-      </c>
       <c r="D4" s="1">
         <v>45427</v>
       </c>
